--- a/ais-w26.xlsx
+++ b/ais-w26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenlo\Desktop\2526_Winter_SFQ_Data\File Upload to AQA website\Regen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A416BB0F-A29D-472F-A14D-C27FE468C548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{A416BB0F-A29D-472F-A14D-C27FE468C548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{849C2A41-8B65-449C-9B89-76AFC565FDD3}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{B1401512-9E9C-4803-B64E-C401C65E7126}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B1401512-9E9C-4803-B64E-C401C65E7126}"/>
   </bookViews>
   <sheets>
     <sheet name="School_Term_Summary_Report-AIS-" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
   <si>
     <t>Academic Year</t>
   </si>
@@ -73,34 +73,19 @@
     <t>Low Response Rate Indicator</t>
   </si>
   <si>
-    <t>Response Rate (Adjusted)</t>
-  </si>
-  <si>
     <t>No. of Sections Evaluated</t>
   </si>
   <si>
     <t>Course Overall - Mean</t>
   </si>
   <si>
-    <t>Course Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Course Overall - SD</t>
   </si>
   <si>
-    <t>Course Overall - SD (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - Mean</t>
   </si>
   <si>
-    <t>Instructor Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - SD</t>
-  </si>
-  <si>
-    <t>Instructor Overall - SD (Adjusted)</t>
   </si>
   <si>
     <t>25-26</t>
@@ -1098,10 +1083,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022CBC0E-3BD6-4AEA-B6CC-8E13C9A82676}">
-  <dimension ref="A1:AA30"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1168,401 +1153,386 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.50900000000000001</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.87</v>
       </c>
       <c r="T2">
-        <v>4.87</v>
+        <v>0.39</v>
+      </c>
+      <c r="U2">
+        <v>4.8099999999999996</v>
       </c>
       <c r="V2">
-        <v>0.39</v>
-      </c>
-      <c r="X2">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="Z2">
         <v>0.47</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.49399999999999999</v>
       </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
       <c r="S3">
-        <v>2</v>
+        <v>4.91</v>
       </c>
       <c r="T3">
+        <v>0.37</v>
+      </c>
+      <c r="U3">
         <v>4.91</v>
       </c>
       <c r="V3">
         <v>0.37</v>
       </c>
-      <c r="X3">
-        <v>4.91</v>
-      </c>
-      <c r="Z3">
-        <v>0.37</v>
-      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.5</v>
       </c>
       <c r="Q4" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>5</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
-      <c r="X4">
-        <v>5</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P5" s="1">
         <v>0.6</v>
       </c>
       <c r="Q5" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T5">
-        <v>4.67</v>
+        <v>0.5</v>
+      </c>
+      <c r="U5">
+        <v>4.5599999999999996</v>
       </c>
       <c r="V5">
-        <v>0.5</v>
-      </c>
-      <c r="X5">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="Z5">
         <v>0.62</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P6" s="1">
         <v>0.40899999999999997</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="T6">
-        <v>4.8899999999999997</v>
+        <v>0.47</v>
+      </c>
+      <c r="U6">
+        <v>4.9400000000000004</v>
       </c>
       <c r="V6">
-        <v>0.47</v>
-      </c>
-      <c r="X6">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="Z6">
         <v>0.24</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
         <v>32</v>
       </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
       <c r="H7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O7">
         <v>44</v>
@@ -1571,66 +1541,66 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="Q7" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="T7">
+        <v>0.47</v>
+      </c>
+      <c r="U7">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
         <v>34</v>
       </c>
-      <c r="S7" t="s">
-        <v>30</v>
-      </c>
-      <c r="T7">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="V7">
-        <v>0.47</v>
-      </c>
-      <c r="X7">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="Z7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" t="s">
+      <c r="M8" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" t="s">
         <v>39</v>
-      </c>
-      <c r="I8" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N8" t="s">
-        <v>44</v>
       </c>
       <c r="O8">
         <v>44</v>
@@ -1639,131 +1609,131 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
-      </c>
-      <c r="S8" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8">
+        <v>4.8899999999999997</v>
       </c>
       <c r="T8">
-        <v>4.8899999999999997</v>
+        <v>0.47</v>
+      </c>
+      <c r="U8">
+        <v>4.9400000000000004</v>
       </c>
       <c r="V8">
-        <v>0.47</v>
-      </c>
-      <c r="X8">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="Z8">
         <v>0.24</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P9" s="1">
         <v>0.58099999999999996</v>
       </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
       <c r="S9">
-        <v>1</v>
+        <v>4.92</v>
       </c>
       <c r="T9">
-        <v>4.92</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U9">
+        <v>4.88</v>
       </c>
       <c r="V9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="X9">
-        <v>4.88</v>
-      </c>
-      <c r="Z9">
         <v>0.44</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O10">
         <v>43</v>
@@ -1771,64 +1741,64 @@
       <c r="P10" s="1">
         <v>0.58099999999999996</v>
       </c>
-      <c r="S10" t="s">
-        <v>30</v>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10">
+        <v>4.92</v>
       </c>
       <c r="T10">
-        <v>4.92</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U10">
+        <v>4.88</v>
       </c>
       <c r="V10">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="X10">
-        <v>4.88</v>
-      </c>
-      <c r="Z10">
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
         <v>41</v>
       </c>
-      <c r="D11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="J11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" t="s">
         <v>45</v>
-      </c>
-      <c r="H11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" t="s">
-        <v>46</v>
-      </c>
-      <c r="J11" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L11" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11" t="s">
-        <v>50</v>
       </c>
       <c r="O11">
         <v>43</v>
@@ -1836,132 +1806,132 @@
       <c r="P11" s="1">
         <v>0.58099999999999996</v>
       </c>
-      <c r="S11" t="s">
-        <v>30</v>
+      <c r="R11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11">
+        <v>4.92</v>
       </c>
       <c r="T11">
-        <v>4.92</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="U11">
+        <v>4.88</v>
       </c>
       <c r="V11">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="X11">
-        <v>4.88</v>
-      </c>
-      <c r="Z11">
         <v>0.44</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" t="s">
-        <v>33</v>
-      </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G12">
         <v>3350</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P12" s="1">
         <v>0.5</v>
       </c>
       <c r="Q12" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
         <v>5</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
-      <c r="X12">
-        <v>5</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G13">
         <v>3350</v>
       </c>
       <c r="H13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1970,66 +1940,66 @@
         <v>0.5</v>
       </c>
       <c r="Q13" t="s">
-        <v>34</v>
-      </c>
-      <c r="S13" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <v>5</v>
       </c>
       <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>5</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
-      <c r="X13">
-        <v>5</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" t="s">
-        <v>33</v>
-      </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>3350</v>
       </c>
       <c r="H14" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -2038,134 +2008,134 @@
         <v>0.5</v>
       </c>
       <c r="Q14" t="s">
-        <v>34</v>
-      </c>
-      <c r="S14" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R14" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14">
+        <v>5</v>
       </c>
       <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
         <v>5</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
-      <c r="X14">
-        <v>5</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1">
         <v>0.6</v>
       </c>
       <c r="Q15" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T15">
-        <v>4.67</v>
+        <v>0.5</v>
+      </c>
+      <c r="U15">
+        <v>4.5599999999999996</v>
       </c>
       <c r="V15">
-        <v>0.5</v>
-      </c>
-      <c r="X15">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="Z15">
         <v>0.62</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O16">
         <v>15</v>
@@ -2174,66 +2144,66 @@
         <v>0.6</v>
       </c>
       <c r="Q16" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16">
+        <v>4.67</v>
+      </c>
+      <c r="T16">
+        <v>0.5</v>
+      </c>
+      <c r="U16">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="V16">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
         <v>34</v>
       </c>
-      <c r="S16" t="s">
-        <v>30</v>
-      </c>
-      <c r="T16">
-        <v>4.67</v>
-      </c>
-      <c r="V16">
-        <v>0.5</v>
-      </c>
-      <c r="X16">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="Z16">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="I17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" t="s">
         <v>56</v>
-      </c>
-      <c r="H17" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" t="s">
-        <v>57</v>
-      </c>
-      <c r="J17" t="s">
-        <v>58</v>
-      </c>
-      <c r="K17" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" t="s">
-        <v>59</v>
-      </c>
-      <c r="M17" t="s">
-        <v>60</v>
-      </c>
-      <c r="N17" t="s">
-        <v>61</v>
       </c>
       <c r="O17">
         <v>15</v>
@@ -2242,66 +2212,66 @@
         <v>0.6</v>
       </c>
       <c r="Q17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R17" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17">
+        <v>4.67</v>
+      </c>
+      <c r="T17">
+        <v>0.5</v>
+      </c>
+      <c r="U17">
+        <v>4.22</v>
+      </c>
+      <c r="V17">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" t="s">
         <v>34</v>
       </c>
-      <c r="S17" t="s">
-        <v>30</v>
-      </c>
-      <c r="T17">
-        <v>4.67</v>
-      </c>
-      <c r="V17">
-        <v>0.5</v>
-      </c>
-      <c r="X17">
-        <v>4.22</v>
-      </c>
-      <c r="Z17">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G18" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" t="s">
-        <v>39</v>
-      </c>
       <c r="I18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" t="s">
+        <v>53</v>
+      </c>
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" t="s">
         <v>57</v>
       </c>
-      <c r="J18" t="s">
+      <c r="N18" t="s">
         <v>58</v>
-      </c>
-      <c r="K18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" t="s">
-        <v>59</v>
-      </c>
-      <c r="M18" t="s">
-        <v>62</v>
-      </c>
-      <c r="N18" t="s">
-        <v>63</v>
       </c>
       <c r="O18">
         <v>15</v>
@@ -2310,65 +2280,65 @@
         <v>0.6</v>
       </c>
       <c r="Q18" t="s">
-        <v>34</v>
-      </c>
-      <c r="S18" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18">
+        <v>4.67</v>
       </c>
       <c r="T18">
-        <v>4.67</v>
+        <v>0.5</v>
+      </c>
+      <c r="U18">
+        <v>4.8899999999999997</v>
       </c>
       <c r="V18">
-        <v>0.5</v>
-      </c>
-      <c r="X18">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="Z18">
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>46082</v>
       </c>
@@ -2379,6 +2349,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -2627,15 +2606,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2648,13 +2618,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BD678CF-24AF-49BE-BB59-AA688CA14242}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2A977E-D78C-4A42-814B-3154CDDAF46F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2A977E-D78C-4A42-814B-3154CDDAF46F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BD678CF-24AF-49BE-BB59-AA688CA14242}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC38BE1B-CF60-4F28-A584-0E002F26FD9A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC38BE1B-CF60-4F28-A584-0E002F26FD9A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ais-w26.xlsx
+++ b/ais-w26.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A416BB0F-A29D-472F-A14D-C27FE468C548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{849C2A41-8B65-449C-9B89-76AFC565FDD3}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{D0943B63-3323-4B10-8216-53779DB96697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2B2B8B-B733-4BFB-BBFF-0BB989A48A23}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B1401512-9E9C-4803-B64E-C401C65E7126}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C429A769-4EDE-4A0A-9D63-416BE87B9178}"/>
   </bookViews>
   <sheets>
-    <sheet name="School_Term_Summary_Report-AIS-" sheetId="1" r:id="rId1"/>
+    <sheet name="ais-w26" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="68">
   <si>
     <t>Academic Year</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Low Response Rate Indicator</t>
+  </si>
+  <si>
+    <t>Response Rate (Adjusted)</t>
   </si>
   <si>
     <t>No. of Sections Evaluated</t>
@@ -1082,11 +1085,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022CBC0E-3BD6-4AEA-B6CC-8E13C9A82676}">
-  <dimension ref="A1:V30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A5C672-6E72-4843-9EC1-374F177CF9C3}">
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1153,386 +1156,389 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" s="1">
         <v>0.50900000000000001</v>
       </c>
       <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2">
+        <v>4</v>
+      </c>
+      <c r="T2">
+        <v>4.87</v>
+      </c>
+      <c r="U2">
+        <v>0.39</v>
+      </c>
+      <c r="V2">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="W2">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="R2">
-        <v>4</v>
-      </c>
-      <c r="S2">
-        <v>4.87</v>
-      </c>
-      <c r="T2">
-        <v>0.39</v>
-      </c>
-      <c r="U2">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="V2">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="1">
         <v>0.49399999999999999</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>2</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>4.91</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>0.37</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>4.91</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>0.37</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" s="1">
         <v>0.5</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4">
+        <v>30</v>
+      </c>
+      <c r="S4">
         <v>1</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>5</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>0</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>5</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" s="1">
         <v>0.6</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5">
+        <v>30</v>
+      </c>
+      <c r="S5">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>4.67</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>0.5</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>4.5599999999999996</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>0.62</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" s="1">
         <v>0.40899999999999997</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6">
+        <v>30</v>
+      </c>
+      <c r="S6">
         <v>1</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>4.8899999999999997</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>0.47</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>4.9400000000000004</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>0.24</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
         <v>34</v>
       </c>
-      <c r="I7" t="s">
-        <v>33</v>
-      </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7">
         <v>44</v>
@@ -1541,66 +1547,66 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" t="s">
+        <v>30</v>
+      </c>
+      <c r="S7" t="s">
+        <v>26</v>
+      </c>
+      <c r="T7">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="U7">
+        <v>0.47</v>
+      </c>
+      <c r="V7">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="W7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
         <v>25</v>
       </c>
-      <c r="S7">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="T7">
-        <v>0.47</v>
-      </c>
-      <c r="U7">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="V7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" t="s">
-        <v>35</v>
-      </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O8">
         <v>44</v>
@@ -1609,131 +1615,131 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" t="s">
+        <v>30</v>
+      </c>
+      <c r="S8" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="U8">
+        <v>0.47</v>
+      </c>
+      <c r="V8">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="W8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="S8">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="T8">
-        <v>0.47</v>
-      </c>
-      <c r="U8">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="V8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P9" s="1">
         <v>0.58099999999999996</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>1</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>4.92</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>0.28000000000000003</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>4.88</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>0.44</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O10">
         <v>43</v>
@@ -1741,64 +1747,64 @@
       <c r="P10" s="1">
         <v>0.58099999999999996</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
+        <v>26</v>
+      </c>
+      <c r="T10">
+        <v>4.92</v>
+      </c>
+      <c r="U10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V10">
+        <v>4.88</v>
+      </c>
+      <c r="W10">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="S10">
-        <v>4.92</v>
-      </c>
-      <c r="T10">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="U10">
-        <v>4.88</v>
-      </c>
-      <c r="V10">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O11">
         <v>43</v>
@@ -1806,132 +1812,132 @@
       <c r="P11" s="1">
         <v>0.58099999999999996</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11">
+        <v>4.92</v>
+      </c>
+      <c r="U11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V11">
+        <v>4.88</v>
+      </c>
+      <c r="W11">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
         <v>25</v>
       </c>
-      <c r="S11">
-        <v>4.92</v>
-      </c>
-      <c r="T11">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="U11">
-        <v>4.88</v>
-      </c>
-      <c r="V11">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
-      </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12">
         <v>3350</v>
       </c>
       <c r="H12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P12" s="1">
         <v>0.5</v>
       </c>
       <c r="Q12" t="s">
-        <v>29</v>
-      </c>
-      <c r="R12">
+        <v>30</v>
+      </c>
+      <c r="S12">
         <v>1</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>5</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>0</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>5</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <v>3350</v>
       </c>
       <c r="H13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1940,66 +1946,66 @@
         <v>0.5</v>
       </c>
       <c r="Q13" t="s">
+        <v>30</v>
+      </c>
+      <c r="S13" t="s">
+        <v>26</v>
+      </c>
+      <c r="T13">
+        <v>5</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>5</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
         <v>29</v>
       </c>
-      <c r="R13" t="s">
-        <v>25</v>
-      </c>
-      <c r="S13">
-        <v>5</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>5</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14">
         <v>3350</v>
       </c>
       <c r="H14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -2008,134 +2014,134 @@
         <v>0.5</v>
       </c>
       <c r="Q14" t="s">
-        <v>29</v>
-      </c>
-      <c r="R14" t="s">
+        <v>30</v>
+      </c>
+      <c r="S14" t="s">
+        <v>26</v>
+      </c>
+      <c r="T14">
+        <v>5</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>5</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
         <v>25</v>
       </c>
-      <c r="S14">
-        <v>5</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>5</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>31</v>
       </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" t="s">
-        <v>30</v>
-      </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P15" s="1">
         <v>0.6</v>
       </c>
       <c r="Q15" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15">
+        <v>30</v>
+      </c>
+      <c r="S15">
         <v>1</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>4.67</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>0.5</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>4.5599999999999996</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>0.62</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O16">
         <v>15</v>
@@ -2144,66 +2150,66 @@
         <v>0.6</v>
       </c>
       <c r="Q16" t="s">
-        <v>29</v>
-      </c>
-      <c r="R16" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16">
+        <v>4.67</v>
+      </c>
+      <c r="U16">
+        <v>0.5</v>
+      </c>
+      <c r="V16">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="W16">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s">
         <v>25</v>
       </c>
-      <c r="S16">
-        <v>4.67</v>
-      </c>
-      <c r="T16">
-        <v>0.5</v>
-      </c>
-      <c r="U16">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="V16">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O17">
         <v>15</v>
@@ -2212,66 +2218,66 @@
         <v>0.6</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
-      </c>
-      <c r="R17" t="s">
+        <v>30</v>
+      </c>
+      <c r="S17" t="s">
+        <v>26</v>
+      </c>
+      <c r="T17">
+        <v>4.67</v>
+      </c>
+      <c r="U17">
+        <v>0.5</v>
+      </c>
+      <c r="V17">
+        <v>4.22</v>
+      </c>
+      <c r="W17">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" t="s">
         <v>25</v>
       </c>
-      <c r="S17">
-        <v>4.67</v>
-      </c>
-      <c r="T17">
-        <v>0.5</v>
-      </c>
-      <c r="U17">
-        <v>4.22</v>
-      </c>
-      <c r="V17">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" t="s">
-        <v>24</v>
-      </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O18">
         <v>15</v>
@@ -2280,67 +2286,67 @@
         <v>0.6</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
-      </c>
-      <c r="R18" t="s">
-        <v>25</v>
-      </c>
-      <c r="S18">
+        <v>30</v>
+      </c>
+      <c r="S18" t="s">
+        <v>26</v>
+      </c>
+      <c r="T18">
         <v>4.67</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>0.5</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>4.8899999999999997</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46082</v>
+        <v>46094</v>
       </c>
     </row>
   </sheetData>
@@ -2358,6 +2364,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="307c76f0-d205-4835-9aae-d70c69349486">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -2606,19 +2623,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="307c76f0-d205-4835-9aae-d70c69349486">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA2A977E-D78C-4A42-814B-3154CDDAF46F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F114F72E-8565-4F1D-9205-7E7483AF4112}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -2626,7 +2632,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BD678CF-24AF-49BE-BB59-AA688CA14242}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DAEACC4-4211-42CD-9776-81A991EC9126}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A5830CF-ADD7-44D5-B960-AB11537CEF47}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -2642,15 +2659,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC38BE1B-CF60-4F28-A584-0E002F26FD9A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
-    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ais-w26.xlsx
+++ b/ais-w26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{D0943B63-3323-4B10-8216-53779DB96697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF2B2B8B-B733-4BFB-BBFF-0BB989A48A23}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{D0943B63-3323-4B10-8216-53779DB96697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4FE13C2-CABA-40C9-A3BD-DA6500D68F1E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C429A769-4EDE-4A0A-9D63-416BE87B9178}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
   <si>
     <t>Academic Year</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Low Response Rate Indicator</t>
-  </si>
-  <si>
-    <t>Response Rate (Adjusted)</t>
   </si>
   <si>
     <t>No. of Sections Evaluated</t>
@@ -1086,10 +1083,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A5C672-6E72-4843-9EC1-374F177CF9C3}">
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1156,389 +1153,386 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.50900000000000001</v>
       </c>
       <c r="Q2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>4</v>
+      </c>
+      <c r="S2">
+        <v>4.87</v>
+      </c>
+      <c r="T2">
+        <v>0.39</v>
+      </c>
+      <c r="U2">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="V2">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="S2">
-        <v>4</v>
-      </c>
-      <c r="T2">
-        <v>4.87</v>
-      </c>
-      <c r="U2">
-        <v>0.39</v>
-      </c>
-      <c r="V2">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="W2">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.49399999999999999</v>
       </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
       <c r="S3">
-        <v>2</v>
+        <v>4.91</v>
       </c>
       <c r="T3">
+        <v>0.37</v>
+      </c>
+      <c r="U3">
         <v>4.91</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>0.37</v>
       </c>
-      <c r="V3">
-        <v>4.91</v>
-      </c>
-      <c r="W3">
-        <v>0.37</v>
-      </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.5</v>
       </c>
       <c r="Q4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>5</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
         <v>30</v>
       </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
-      <c r="T4">
-        <v>5</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>5</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5" s="1">
         <v>0.6</v>
       </c>
       <c r="Q5" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T5">
-        <v>4.67</v>
+        <v>0.5</v>
       </c>
       <c r="U5">
-        <v>0.5</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="V5">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="W5">
         <v>0.62</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
         <v>33</v>
       </c>
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
-      </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P6" s="1">
         <v>0.40899999999999997</v>
       </c>
       <c r="Q6" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="T6">
-        <v>4.8899999999999997</v>
+        <v>0.47</v>
       </c>
       <c r="U6">
-        <v>0.47</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="V6">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="W6">
         <v>0.24</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
         <v>33</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" t="s">
         <v>35</v>
       </c>
-      <c r="I7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" t="s">
-        <v>36</v>
-      </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O7">
         <v>44</v>
@@ -1547,66 +1541,66 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="Q7" t="s">
-        <v>30</v>
-      </c>
-      <c r="S7" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7">
+        <v>4.8899999999999997</v>
       </c>
       <c r="T7">
-        <v>4.8899999999999997</v>
+        <v>0.47</v>
       </c>
       <c r="U7">
-        <v>0.47</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="V7">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="W7">
         <v>0.24</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>38</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>39</v>
-      </c>
-      <c r="N8" t="s">
-        <v>40</v>
       </c>
       <c r="O8">
         <v>44</v>
@@ -1615,131 +1609,131 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="Q8" t="s">
-        <v>30</v>
-      </c>
-      <c r="S8" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8">
+        <v>4.8899999999999997</v>
       </c>
       <c r="T8">
-        <v>4.8899999999999997</v>
+        <v>0.47</v>
       </c>
       <c r="U8">
-        <v>0.47</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="V8">
-        <v>4.9400000000000004</v>
-      </c>
-      <c r="W8">
         <v>0.24</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" t="s">
         <v>41</v>
       </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s">
-        <v>42</v>
-      </c>
       <c r="J9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P9" s="1">
         <v>0.58099999999999996</v>
       </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
       <c r="S9">
-        <v>1</v>
+        <v>4.92</v>
       </c>
       <c r="T9">
-        <v>4.92</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="U9">
-        <v>0.28000000000000003</v>
+        <v>4.88</v>
       </c>
       <c r="V9">
-        <v>4.88</v>
-      </c>
-      <c r="W9">
         <v>0.44</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
         <v>41</v>
       </c>
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>42</v>
       </c>
-      <c r="J10" t="s">
-        <v>43</v>
-      </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O10">
         <v>43</v>
@@ -1747,64 +1741,64 @@
       <c r="P10" s="1">
         <v>0.58099999999999996</v>
       </c>
-      <c r="S10" t="s">
-        <v>26</v>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10">
+        <v>4.92</v>
       </c>
       <c r="T10">
-        <v>4.92</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="U10">
-        <v>0.28000000000000003</v>
+        <v>4.88</v>
       </c>
       <c r="V10">
-        <v>4.88</v>
-      </c>
-      <c r="W10">
         <v>0.44</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
         <v>41</v>
       </c>
-      <c r="H11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>42</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
         <v>43</v>
       </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>44</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>45</v>
-      </c>
-      <c r="N11" t="s">
-        <v>46</v>
       </c>
       <c r="O11">
         <v>43</v>
@@ -1812,132 +1806,132 @@
       <c r="P11" s="1">
         <v>0.58099999999999996</v>
       </c>
-      <c r="S11" t="s">
-        <v>26</v>
+      <c r="R11" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11">
+        <v>4.92</v>
       </c>
       <c r="T11">
-        <v>4.92</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="U11">
-        <v>0.28000000000000003</v>
+        <v>4.88</v>
       </c>
       <c r="V11">
-        <v>4.88</v>
-      </c>
-      <c r="W11">
         <v>0.44</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12">
         <v>3350</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P12" s="1">
         <v>0.5</v>
       </c>
       <c r="Q12" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
         <v>5</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>0</v>
       </c>
-      <c r="V12">
-        <v>5</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
         <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13">
         <v>3350</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" t="s">
         <v>47</v>
       </c>
-      <c r="J13" t="s">
-        <v>48</v>
-      </c>
       <c r="K13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1946,66 +1940,66 @@
         <v>0.5</v>
       </c>
       <c r="Q13" t="s">
-        <v>30</v>
-      </c>
-      <c r="S13" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <v>5</v>
       </c>
       <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
         <v>5</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>5</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
         <v>23</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
         <v>24</v>
       </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>3350</v>
       </c>
       <c r="H14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" t="s">
         <v>47</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
         <v>48</v>
       </c>
-      <c r="K14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>49</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>50</v>
-      </c>
-      <c r="N14" t="s">
-        <v>51</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -2014,134 +2008,134 @@
         <v>0.5</v>
       </c>
       <c r="Q14" t="s">
+        <v>29</v>
+      </c>
+      <c r="R14" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14">
+        <v>5</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>5</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>30</v>
       </c>
-      <c r="S14" t="s">
-        <v>26</v>
-      </c>
-      <c r="T14">
-        <v>5</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>5</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" t="s">
         <v>52</v>
       </c>
-      <c r="H15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I15" t="s">
-        <v>53</v>
-      </c>
       <c r="J15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" s="1">
         <v>0.6</v>
       </c>
       <c r="Q15" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T15">
-        <v>4.67</v>
+        <v>0.5</v>
       </c>
       <c r="U15">
-        <v>0.5</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="V15">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="W15">
         <v>0.62</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
         <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" t="s">
         <v>52</v>
       </c>
-      <c r="H16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>53</v>
       </c>
-      <c r="J16" t="s">
-        <v>54</v>
-      </c>
       <c r="K16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O16">
         <v>15</v>
@@ -2150,66 +2144,66 @@
         <v>0.6</v>
       </c>
       <c r="Q16" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16">
+        <v>4.67</v>
+      </c>
+      <c r="T16">
+        <v>0.5</v>
+      </c>
+      <c r="U16">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="V16">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
         <v>30</v>
       </c>
-      <c r="S16" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16">
-        <v>4.67</v>
-      </c>
-      <c r="U16">
-        <v>0.5</v>
-      </c>
-      <c r="V16">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="W16">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" t="s">
         <v>52</v>
       </c>
-      <c r="H17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="J17" t="s">
         <v>53</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" t="s">
         <v>54</v>
       </c>
-      <c r="K17" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>56</v>
-      </c>
-      <c r="N17" t="s">
-        <v>57</v>
       </c>
       <c r="O17">
         <v>15</v>
@@ -2218,66 +2212,66 @@
         <v>0.6</v>
       </c>
       <c r="Q17" t="s">
+        <v>29</v>
+      </c>
+      <c r="R17" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17">
+        <v>4.67</v>
+      </c>
+      <c r="T17">
+        <v>0.5</v>
+      </c>
+      <c r="U17">
+        <v>4.22</v>
+      </c>
+      <c r="V17">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
         <v>30</v>
       </c>
-      <c r="S17" t="s">
-        <v>26</v>
-      </c>
-      <c r="T17">
-        <v>4.67</v>
-      </c>
-      <c r="U17">
-        <v>0.5</v>
-      </c>
-      <c r="V17">
-        <v>4.22</v>
-      </c>
-      <c r="W17">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>31</v>
-      </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" t="s">
         <v>52</v>
       </c>
-      <c r="H18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>53</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" t="s">
         <v>54</v>
       </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="s">
-        <v>55</v>
-      </c>
       <c r="M18" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" t="s">
         <v>58</v>
-      </c>
-      <c r="N18" t="s">
-        <v>59</v>
       </c>
       <c r="O18">
         <v>15</v>
@@ -2286,65 +2280,65 @@
         <v>0.6</v>
       </c>
       <c r="Q18" t="s">
-        <v>30</v>
-      </c>
-      <c r="S18" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="R18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18">
+        <v>4.67</v>
       </c>
       <c r="T18">
-        <v>4.67</v>
+        <v>0.5</v>
       </c>
       <c r="U18">
-        <v>0.5</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="V18">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="W18">
         <v>0.33</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>46094</v>
       </c>
@@ -2355,15 +2349,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="307c76f0-d205-4835-9aae-d70c69349486">
@@ -2372,6 +2357,15 @@
     <TaxCatchAll xmlns="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2624,20 +2618,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F114F72E-8565-4F1D-9205-7E7483AF4112}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DAEACC4-4211-42CD-9776-81A991EC9126}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
     <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F114F72E-8565-4F1D-9205-7E7483AF4112}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
